--- a/model.xlsx
+++ b/model.xlsx
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>77272</v>
+        <v>77299</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.2878</v>
+        <v>74.27209999999999</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>311.859</v>
+        <v>311.8863</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>99.12</v>
+        <v>99.277</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>100.05</v>
+        <v>102.96</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>77299</v>
+        <v>77792</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.27209999999999</v>
+        <v>74.2462</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>311.8863</v>
+        <v>311.6414</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>99.277</v>
+        <v>99.316</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>102.96</v>
+        <v>102.25</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>77792</v>
+        <v>77550</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.2462</v>
+        <v>74.1986</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>311.6414</v>
+        <v>311.6332</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>15.84</v>
+        <v>17.1</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>82.20999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>99.316</v>
+        <v>99.57899999999999</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>102.25</v>
+        <v>102.87</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>77550</v>
+        <v>77810</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.1986</v>
+        <v>74.35209999999999</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>311.6332</v>
+        <v>312.0104</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>99.57899999999999</v>
+        <v>99.60299999999999</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>102.87</v>
+        <v>102.99</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>77810</v>
+        <v>77632</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.35209999999999</v>
+        <v>74.3351</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>312.0104</v>
+        <v>311.9644</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>83.90000000000001</v>
+        <v>83.70869999999999</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>99.60299999999999</v>
+        <v>99.65000000000001</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>102.99</v>
+        <v>104.42</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>77632</v>
+        <v>75994</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.3351</v>
+        <v>73.7368</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>311.9644</v>
+        <v>311.0377</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>83.70869999999999</v>
+        <v>83.70999999999999</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>99.65000000000001</v>
+        <v>99.60599999999999</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>104.42</v>
+        <v>104.71</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>75994</v>
+        <v>75880</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>73.7368</v>
+        <v>73.6995</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>311.0377</v>
+        <v>311.0369</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>17.2</v>
+        <v>17.71</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>83.70999999999999</v>
+        <v>80.7276</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>99.60599999999999</v>
+        <v>100.323</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>104.71</v>
+        <v>102.32</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>75880</v>
+        <v>76409</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>73.6995</v>
+        <v>73.66889999999999</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>311.0369</v>
+        <v>311.082</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>80.7276</v>
+        <v>80.73</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>100.323</v>
+        <v>100.268</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>102.32</v>
+        <v>101.77</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>76409</v>
+        <v>76306</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>73.66889999999999</v>
+        <v>73.6754</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>311.082</v>
+        <v>311.0604</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>17.71</v>
+        <v>15.44</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>80.73</v>
+        <v>76.2178</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>100.268</v>
+        <v>100.273</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>101.77</v>
+        <v>101.34</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>76306</v>
+        <v>77051</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>73.6754</v>
+        <v>73.869</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>311.0604</v>
+        <v>310.9936</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>76.2178</v>
+        <v>76.22</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>100.273</v>
+        <v>100.311</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>101.34</v>
+        <v>101.01</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>77051</v>
+        <v>77529</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>73.869</v>
+        <v>73.83159999999999</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>310.9936</v>
+        <v>310.9927</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>15.44</v>
+        <v>14.81</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>76.22</v>
+        <v>80.63500000000001</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>100.311</v>
+        <v>100.215</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>101.01</v>
+        <v>95.47</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>77529</v>
+        <v>81306</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>73.83159999999999</v>
+        <v>74.3289</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>310.9927</v>
+        <v>311.6777</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>80.63500000000001</v>
+        <v>80.64</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>100.215</v>
+        <v>100.22</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>95.47</v>
+        <v>100.3</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>81306</v>
+        <v>81061</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.3289</v>
+        <v>74.3017</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>311.6777</v>
+        <v>311.6704</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14092,7 +14092,7 @@
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14317,7 +14317,7 @@
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>81061</v>
+        <v>80463</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.3017</v>
+        <v>74.2244</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>311.6704</v>
+        <v>311.5719</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>100.3</v>
+        <v>96.08</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>80463</v>
+        <v>80456</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.2244</v>
+        <v>74.20950000000001</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>311.5719</v>
+        <v>311.5761</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>100.22</v>
+        <v>100.302</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>96.08</v>
+        <v>93.97</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>80456</v>
+        <v>81374</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.20950000000001</v>
+        <v>74.2225</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>311.5761</v>
+        <v>311.7818</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>100.302</v>
+        <v>100.327</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>93.97</v>
+        <v>94.59</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>81374</v>
+        <v>81610</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.2225</v>
+        <v>74.22280000000001</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>311.7818</v>
+        <v>311.7648</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>14.81</v>
+        <v>14.87</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>80.64</v>
+        <v>81.1974</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>100.327</v>
+        <v>100.395</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>94.59</v>
+        <v>93.19</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>81610</v>
+        <v>85465</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.22280000000001</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>311.7648</v>
+        <v>313.4118</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>81.1974</v>
+        <v>81.2</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>100.395</v>
+        <v>100.366</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>93.19</v>
+        <v>93.39</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>85465</v>
+        <v>85368</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.73999999999999</v>
+        <v>74.71599999999999</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.4118</v>
+        <v>313.4169</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>14.87</v>
+        <v>14.21</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>81.2</v>
+        <v>78.56</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>100.366</v>
+        <v>100.68</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>93.39</v>
+        <v>89.81</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>85368</v>
+        <v>86506</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.71599999999999</v>
+        <v>75.26349999999999</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.4169</v>
+        <v>313.3185</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14008,11 +14008,11 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>14.21</v>
+        <v>14.87</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
@@ -14033,11 +14033,11 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>78.56</v>
+        <v>81.2</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
@@ -14062,7 +14062,7 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>100.68</v>
+        <v>100.709</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>89.81</v>
+        <v>89.45</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>86506</v>
+        <v>86720</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>75.26349999999999</v>
+        <v>75.2658</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.3185</v>
+        <v>313.3081</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>14.87</v>
+        <v>15.18</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>81.2</v>
+        <v>95.45269999999999</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>100.709</v>
+        <v>101.077</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>89.45</v>
+        <v>91.3</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>86720</v>
+        <v>84325</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>75.2658</v>
+        <v>75.31789999999999</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.3081</v>
+        <v>312.5812</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>95.45269999999999</v>
+        <v>95.45</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.077</v>
+        <v>101.134</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>91.3</v>
+        <v>92.02</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>84325</v>
+        <v>83940</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>75.31789999999999</v>
+        <v>75.41</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>312.5812</v>
+        <v>312.5633</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>15.18</v>
+        <v>15.67</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>95.45</v>
+        <v>104.5805</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.134</v>
+        <v>101.282</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>92.02</v>
+        <v>92.92</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>83940</v>
+        <v>84212</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>75.41</v>
+        <v>75.4395</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>312.5633</v>
+        <v>313.8747</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>104.5805</v>
+        <v>104.58</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.282</v>
+        <v>101.227</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>92.92</v>
+        <v>92.64</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>84212</v>
+        <v>84183</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>75.4395</v>
+        <v>75.3717</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.8747</v>
+        <v>313.8788</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>15.67</v>
+        <v>14.87</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>104.58</v>
+        <v>96.0025</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.227</v>
+        <v>101.035</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>92.64</v>
+        <v>92.44</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>84183</v>
+        <v>84017</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>75.3717</v>
+        <v>75.34269999999999</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.8788</v>
+        <v>313.2138</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>96.0025</v>
+        <v>96</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.035</v>
+        <v>100.97</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>92.44</v>
+        <v>92.41</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>84017</v>
+        <v>83907</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>75.34269999999999</v>
+        <v>75.4265</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.2138</v>
+        <v>313.2043</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14092,7 +14092,7 @@
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14317,7 +14317,7 @@
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>83907</v>
+        <v>84387</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>75.4265</v>
+        <v>75.2672</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.2043</v>
+        <v>313.1975</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>84387</v>
+        <v>84602</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>75.2672</v>
+        <v>75.2621</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.1975</v>
+        <v>313.1949</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>100.97</v>
+        <v>101.091</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>92.41</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>84602</v>
+        <v>83302</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>75.2621</v>
+        <v>75.1443</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.1949</v>
+        <v>313.0353</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.091</v>
+        <v>101.177</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>93.34999999999999</v>
+        <v>94.05</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>83302</v>
+        <v>83038</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>75.1443</v>
+        <v>75.1926</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.0353</v>
+        <v>313.0155</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>14.87</v>
+        <v>16.07</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>96</v>
+        <v>101.82</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.177</v>
+        <v>101.276</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>94.05</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>83038</v>
+        <v>83076</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>75.1926</v>
+        <v>74.7495</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.0155</v>
+        <v>312.9663</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.276</v>
+        <v>101.259</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>94.15000000000001</v>
+        <v>93.91</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.7495</v>
+        <v>74.6823</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>312.9663</v>
+        <v>312.9587</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>16.07</v>
+        <v>16.04</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>101.82</v>
+        <v>106.6027</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.259</v>
+        <v>101.396</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>93.91</v>
+        <v>89.38</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>83076</v>
+        <v>83268</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.6823</v>
+        <v>74.38930000000001</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>312.9587</v>
+        <v>312.4337</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>106.6027</v>
+        <v>106.6</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.396</v>
+        <v>101.261</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,11 +14308,11 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>89.38</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>83268</v>
+        <v>83126</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.38930000000001</v>
+        <v>74.358</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>312.4337</v>
+        <v>312.879</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>16.04</v>
+        <v>16.34</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>106.6</v>
+        <v>110.45</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.261</v>
+        <v>101.45</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>89.20999999999999</v>
+        <v>90.42</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>83126</v>
+        <v>83756</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.358</v>
+        <v>74.0258</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>312.879</v>
+        <v>312.3287</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14083,11 +14083,11 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.45</v>
+        <v>101.672</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
@@ -14308,11 +14308,11 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>90.42</v>
+        <v>90.47</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>83756</v>
+        <v>84059</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.0258</v>
+        <v>74.027</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>312.3287</v>
+        <v>312.3335</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>16.34</v>
+        <v>16.39</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>110.45</v>
+        <v>108.13</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.672</v>
+        <v>102.1</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>90.47</v>
+        <v>92.87</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>84059</v>
+        <v>85567</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.027</v>
+        <v>74.0384</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>312.3335</v>
+        <v>313.1667</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14083,11 +14083,11 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.1</v>
+        <v>101.884</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
@@ -14308,11 +14308,11 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>92.87</v>
+        <v>91.89</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>85567</v>
+        <v>85977</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.0384</v>
+        <v>73.99039999999999</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.1667</v>
+        <v>313.1352</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>16.39</v>
+        <v>15.31</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>108.13</v>
+        <v>107.2868</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.884</v>
+        <v>101.924</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>91.89</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>85977</v>
+        <v>84650</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>73.99039999999999</v>
+        <v>74.1144</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.1352</v>
+        <v>313.5946</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>107.2868</v>
+        <v>107.29</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.924</v>
+        <v>101.93</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>91.26000000000001</v>
+        <v>91.11</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>84650</v>
+        <v>84627</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.1144</v>
+        <v>74.1159</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.5946</v>
+        <v>313.5952</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14092,7 +14092,7 @@
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14317,7 +14317,7 @@
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>84627</v>
+        <v>84798</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.1159</v>
+        <v>74.0882</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.5952</v>
+        <v>313.6681</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>84798</v>
+        <v>84976</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.0882</v>
+        <v>74.083</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.6681</v>
+        <v>313.6691</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14092,7 +14092,7 @@
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14317,7 +14317,7 @@
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>84976</v>
+        <v>86044</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.083</v>
+        <v>74.08029999999999</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.6691</v>
+        <v>313.8844</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14083,11 +14083,11 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.93</v>
+        <v>102.339</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
@@ -14308,11 +14308,11 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>91.11</v>
+        <v>90.06</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>86044</v>
+        <v>85821</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.08029999999999</v>
+        <v>73.96469999999999</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.8844</v>
+        <v>313.8682</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>15.31</v>
+        <v>15.52</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>107.29</v>
+        <v>113.6</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.339</v>
+        <v>102.169</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>90.06</v>
+        <v>89.86</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>85821</v>
+        <v>85569</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>73.96469999999999</v>
+        <v>74.26179999999999</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.8682</v>
+        <v>314.3417</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.169</v>
+        <v>102.282</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>89.86</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>85569</v>
+        <v>85316</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.26179999999999</v>
+        <v>74.16289999999999</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>314.3417</v>
+        <v>314.3205</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>15.52</v>
+        <v>15.01</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>113.6</v>
+        <v>105.2</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.282</v>
+        <v>102.033</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>88.34999999999999</v>
+        <v>90.26000000000001</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>85316</v>
+        <v>84077</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.16289999999999</v>
+        <v>74.1887</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>314.3205</v>
+        <v>314.5584</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.033</v>
+        <v>102.084</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>90.26000000000001</v>
+        <v>90.11</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>84077</v>
+        <v>84215</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.1887</v>
+        <v>74.1182</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>314.5584</v>
+        <v>314.5718</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>15.01</v>
+        <v>15.08</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>105.2</v>
+        <v>102.56</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.084</v>
+        <v>102.237</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>90.11</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>84215</v>
+        <v>82798</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>74.1182</v>
+        <v>73.6497</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>314.5718</v>
+        <v>313.9921</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.237</v>
+        <v>102.316</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>89.98999999999999</v>
+        <v>91.03</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>82798</v>
+        <v>82960</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>73.6497</v>
+        <v>73.5939</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.9921</v>
+        <v>313.995</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>15.08</v>
+        <v>15.41</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>102.56</v>
+        <v>100.7</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14058,16 +14058,16 @@
         </is>
       </c>
       <c r="B30" s="33" t="n">
-        <v>-3.4221</v>
+        <v>-3.384</v>
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.316</v>
+        <v>102.033</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>91.03</v>
+        <v>90.36</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>82960</v>
+        <v>82382</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>73.5939</v>
+        <v>73.14239999999999</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.995</v>
+        <v>313.2791</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.033</v>
+        <v>102.067</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>90.36</v>
+        <v>90.92</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>82382</v>
+        <v>82492</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>73.14239999999999</v>
+        <v>73.10890000000001</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.2791</v>
+        <v>313.2778</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>15.41</v>
+        <v>14.84</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>100.7</v>
+        <v>98.47</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.067</v>
+        <v>102.21</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>90.92</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>82492</v>
+        <v>82617</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>73.10890000000001</v>
+        <v>72.8875</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.2778</v>
+        <v>312.6877</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>82617</v>
+        <v>82737</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.8875</v>
+        <v>72.8694</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>312.6877</v>
+        <v>312.6851</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14092,7 +14092,7 @@
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14317,7 +14317,7 @@
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>82737</v>
+        <v>82786</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.8694</v>
+        <v>72.97199999999999</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>312.6851</v>
+        <v>312.7715</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>82786</v>
+        <v>83093</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.97199999999999</v>
+        <v>72.9717</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>312.7715</v>
+        <v>312.7654</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.21</v>
+        <v>102.167</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>91.84999999999999</v>
+        <v>90.26000000000001</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>83093</v>
+        <v>83453</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.9717</v>
+        <v>72.9019</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>312.7654</v>
+        <v>312.9883</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.167</v>
+        <v>102.189</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>90.26000000000001</v>
+        <v>91.13</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>83453</v>
+        <v>84121</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.9019</v>
+        <v>72.88549999999999</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>312.9883</v>
+        <v>313.0052</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>14.84</v>
+        <v>15.21</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.189</v>
+        <v>102.432</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>91.13</v>
+        <v>92.55</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>84121</v>
+        <v>83693</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.88549999999999</v>
+        <v>72.66930000000001</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>313.0052</v>
+        <v>312.7141</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14008,11 +14008,11 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>15.21</v>
+        <v>15.61</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.432</v>
+        <v>102.315</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>92.55</v>
+        <v>92.27</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>83693</v>
+        <v>83742</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.66930000000001</v>
+        <v>72.6623</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>312.7141</v>
+        <v>312.7476</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,7 +14008,7 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>15.61</v>
+        <v>15.27</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>98.47</v>
+        <v>101.0918</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14058,16 +14058,16 @@
         </is>
       </c>
       <c r="B30" s="33" t="n">
-        <v>-3.384</v>
+        <v>-3.1694</v>
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.315</v>
+        <v>102.089</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>92.27</v>
+        <v>94.84999999999999</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>83742</v>
+        <v>83725</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.6623</v>
+        <v>73.0284</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>312.7476</v>
+        <v>312.9116</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>101.0918</v>
+        <v>101.09</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.089</v>
+        <v>102.117</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>94.84999999999999</v>
+        <v>94.66</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>83725</v>
+        <v>83402</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>73.0284</v>
+        <v>72.9901</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>312.9116</v>
+        <v>312.901</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>15.27</v>
+        <v>16.87</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>101.09</v>
+        <v>99.0643</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.117</v>
+        <v>101.914</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>94.66</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>83402</v>
+        <v>81144</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.9901</v>
+        <v>72.67440000000001</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>312.901</v>
+        <v>307.2618</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>99.0643</v>
+        <v>99.06</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.914</v>
+        <v>102.11</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>93.84999999999999</v>
+        <v>94.34</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>81144</v>
+        <v>80949</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.67440000000001</v>
+        <v>72.7017</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>307.2618</v>
+        <v>307.2565</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>16.87</v>
+        <v>16.46</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>99.06</v>
+        <v>102.4871</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.11</v>
+        <v>101.978</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>94.34</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>80949</v>
+        <v>82021</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.7017</v>
+        <v>72.5669</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>307.2565</v>
+        <v>306.891</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>102.4871</v>
+        <v>102.49</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.978</v>
+        <v>101.927</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>95.84999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>82021</v>
+        <v>82118</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.5669</v>
+        <v>72.70529999999999</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>306.891</v>
+        <v>306.9163</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>16.46</v>
+        <v>19.99</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>102.49</v>
+        <v>101.1029</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.927</v>
+        <v>101.779</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>95.92</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>82118</v>
+        <v>81393</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.70529999999999</v>
+        <v>72.6199</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>306.9163</v>
+        <v>306.5984</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>101.1029</v>
+        <v>101.1</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.779</v>
+        <v>101.84</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>99.04000000000001</v>
+        <v>101.41</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>81393</v>
+        <v>81509</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.6199</v>
+        <v>72.57380000000001</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>306.5984</v>
+        <v>306.5848</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14092,7 +14092,7 @@
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14317,7 +14317,7 @@
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>81509</v>
+        <v>81736</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.57380000000001</v>
+        <v>72.5209</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>306.5848</v>
+        <v>306.3691</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>101.41</v>
+        <v>99.02</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>81736</v>
+        <v>81641</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.5209</v>
+        <v>72.5116</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>306.3691</v>
+        <v>306.3701</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.84</v>
+        <v>101.858</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>99.02</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>81641</v>
+        <v>82557</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.5116</v>
+        <v>72.4704</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>306.3701</v>
+        <v>306.3464</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.858</v>
+        <v>101.816</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>97.51000000000001</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>82557</v>
+        <v>82657</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.4704</v>
+        <v>72.4883</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>306.3464</v>
+        <v>306.3371</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>19.99</v>
+        <v>18.44</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>101.1</v>
+        <v>101.2987</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.816</v>
+        <v>101.842</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>97.31999999999999</v>
+        <v>98.91</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>82657</v>
+        <v>81829</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.4883</v>
+        <v>72.1208</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>306.3371</v>
+        <v>305.4896</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>101.2987</v>
+        <v>101.3</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.842</v>
+        <v>101.774</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>98.91</v>
+        <v>98.81</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>81829</v>
+        <v>81865</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.1208</v>
+        <v>72.1485</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>305.4896</v>
+        <v>305.4897</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>18.44</v>
+        <v>17.31</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>101.3</v>
+        <v>101.695</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.774</v>
+        <v>101.776</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>98.81</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>81865</v>
+        <v>82674</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.1485</v>
+        <v>72.1512</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>305.4897</v>
+        <v>305.227</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>101.695</v>
+        <v>101.7</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.776</v>
+        <v>101.789</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>99.31999999999999</v>
+        <v>99.23</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>82674</v>
+        <v>82567</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.1512</v>
+        <v>72.1272</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>305.227</v>
+        <v>305.186</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>17.31</v>
+        <v>16.68</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>101.7</v>
+        <v>95.94</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.789</v>
+        <v>101.555</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>99.23</v>
+        <v>98.45</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>82567</v>
+        <v>82764</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.1272</v>
+        <v>72.61790000000001</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>305.186</v>
+        <v>305.5045</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.555</v>
+        <v>101.559</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>98.45</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>82764</v>
+        <v>82686</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.61790000000001</v>
+        <v>72.53740000000001</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>305.5045</v>
+        <v>305.5167</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>16.68</v>
+        <v>19.03</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>95.94</v>
+        <v>106.8388</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.559</v>
+        <v>101.654</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>99.04000000000001</v>
+        <v>100</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>82686</v>
+        <v>81653</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.53740000000001</v>
+        <v>72.07429999999999</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>305.5167</v>
+        <v>304.9012</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>106.8388</v>
+        <v>106.84</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.654</v>
+        <v>101.683</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>100</v>
+        <v>100.51</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>81653</v>
+        <v>81767</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.07429999999999</v>
+        <v>72.0585</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>304.9012</v>
+        <v>304.917</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>19.03</v>
+        <v>19.45</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>106.84</v>
+        <v>103.31</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.683</v>
+        <v>101.81</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>100.51</v>
+        <v>103.44</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>81767</v>
+        <v>80883</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>72.0585</v>
+        <v>71.6514</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>304.917</v>
+        <v>304.5744</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>103.44</v>
+        <v>103.27</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>80883</v>
+        <v>80676</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>71.6514</v>
+        <v>71.64109999999999</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>304.5744</v>
+        <v>304.5764</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14092,7 +14092,7 @@
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14317,7 +14317,7 @@
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>80676</v>
+        <v>80882</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>71.64109999999999</v>
+        <v>71.5806</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>304.5764</v>
+        <v>304.3991</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>80882</v>
+        <v>80493</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>71.5806</v>
+        <v>71.5681</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>304.3991</v>
+        <v>304.3922</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.81</v>
+        <v>101.628</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>103.27</v>
+        <v>101.09</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>80493</v>
+        <v>79657</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>71.5681</v>
+        <v>71.51309999999999</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>304.3922</v>
+        <v>304.1302</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.628</v>
+        <v>101.7</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>101.09</v>
+        <v>101.11</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>79657</v>
+        <v>80138</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>71.51309999999999</v>
+        <v>71.468</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>304.1302</v>
+        <v>304.1995</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>19.45</v>
+        <v>18.39</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>103.31</v>
+        <v>102.1914</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.7</v>
+        <v>102.049</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>101.11</v>
+        <v>100.82</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>80138</v>
+        <v>79813</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>71.468</v>
+        <v>71.0425</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>304.1995</v>
+        <v>303.2755</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>102.1914</v>
+        <v>102.19</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.049</v>
+        <v>102.086</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>100.82</v>
+        <v>100.93</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>79813</v>
+        <v>79847</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>71.0425</v>
+        <v>70.95229999999999</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>303.2755</v>
+        <v>303.2707</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>18.39</v>
+        <v>17.52</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>102.19</v>
+        <v>97.874</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.086</v>
+        <v>102.402</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>100.93</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>79847</v>
+        <v>81008</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>70.95229999999999</v>
+        <v>71.11660000000001</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>303.2707</v>
+        <v>303.1918</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14033,7 +14033,7 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>97.874</v>
+        <v>97.87</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.402</v>
+        <v>102.457</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,11 +14308,11 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>99.90000000000001</v>
+        <v>101.68</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>81008</v>
+        <v>80795</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>71.11660000000001</v>
+        <v>71.2158</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>303.1918</v>
+        <v>303.1979</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>17.52</v>
+        <v>16.91</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>97.87</v>
+        <v>94.55</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.457</v>
+        <v>102.143</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>101.68</v>
+        <v>101.45</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>80795</v>
+        <v>79831</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>71.2158</v>
+        <v>71.27030000000001</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>303.1979</v>
+        <v>302.0536</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.143</v>
+        <v>102.231</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>101.45</v>
+        <v>101.42</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>79831</v>
+        <v>79876</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>71.27030000000001</v>
+        <v>71.2345</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>302.0536</v>
+        <v>302.0514</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>16.91</v>
+        <v>17.2</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>94.55</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,16 +14083,16 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>102.231</v>
+        <v>101.752</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,16 +14308,16 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>101.42</v>
+        <v>103.22</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>79876</v>
+        <v>78157</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>71.2345</v>
+        <v>71.25109999999999</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>302.0514</v>
+        <v>301.1725</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.752</v>
+        <v>101.858</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>103.22</v>
+        <v>102.96</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>78157</v>
+        <v>78523</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>71.25109999999999</v>
+        <v>71.262</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>301.1725</v>
+        <v>301.242</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>

--- a/model.xlsx
+++ b/model.xlsx
@@ -13417,7 +13417,7 @@
       </c>
       <c r="B2" s="30" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="C2" s="31" t="n"/>
@@ -14008,16 +14008,16 @@
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>17.2</v>
+        <v>19.42</v>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="E28" s="35" t="inlineStr">
@@ -14033,16 +14033,16 @@
         </is>
       </c>
       <c r="B29" s="33" t="n">
-        <v>93.54000000000001</v>
+        <v>100.2</v>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="E29" s="35" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="E30" s="35" t="inlineStr">
@@ -14083,7 +14083,7 @@
         </is>
       </c>
       <c r="B31" s="33" t="n">
-        <v>101.858</v>
+        <v>101.88</v>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="E31" s="35" t="inlineStr">
@@ -14308,7 +14308,7 @@
         </is>
       </c>
       <c r="B40" s="33" t="n">
-        <v>102.96</v>
+        <v>104.12</v>
       </c>
       <c r="C40" s="34" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="E40" s="35" t="inlineStr">
@@ -14533,16 +14533,16 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>78523</v>
+        <v>77128</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="E49" s="35" t="inlineStr">
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>71.262</v>
+        <v>71.7508</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="E50" s="35" t="inlineStr">
@@ -14583,16 +14583,16 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>301.242</v>
+        <v>300.6259</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="E51" s="35" t="inlineStr">

--- a/model.xlsx
+++ b/model.xlsx
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="B49" s="33" t="n">
-        <v>77128</v>
+        <v>77269</v>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B50" s="33" t="n">
-        <v>71.7508</v>
+        <v>71.83150000000001</v>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="B51" s="33" t="n">
-        <v>300.6259</v>
+        <v>300.668</v>
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
